--- a/downloads/indicadores/EMIM/EMIM_datos.xlsx
+++ b/downloads/indicadores/EMIM/EMIM_datos.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X239"/>
+  <dimension ref="A1:X240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -16371,6 +16371,72 @@
         </is>
       </c>
       <c r="X239" s="11" t="inlineStr">
+        <is>
+          <t>17 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="4" t="inlineStr">
+        <is>
+          <t>Jul 26</t>
+        </is>
+      </c>
+      <c r="B240" s="5" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C240" s="6" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="D240" s="7" t="n">
+        <v>0.01355</v>
+      </c>
+      <c r="E240" s="7" t="n">
+        <v>0.018149</v>
+      </c>
+      <c r="F240" s="7" t="n"/>
+      <c r="G240" s="7" t="n"/>
+      <c r="H240" s="6" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="I240" s="7" t="n">
+        <v>-0.002028</v>
+      </c>
+      <c r="J240" s="7" t="n">
+        <v>-0.013039</v>
+      </c>
+      <c r="K240" s="7" t="n"/>
+      <c r="L240" s="7" t="n"/>
+      <c r="M240" s="6" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="N240" s="7" t="n">
+        <v>0.027607</v>
+      </c>
+      <c r="O240" s="7" t="n">
+        <v>-0.008876</v>
+      </c>
+      <c r="P240" s="7" t="n"/>
+      <c r="Q240" s="7" t="n"/>
+      <c r="R240" s="6" t="n"/>
+      <c r="S240" s="7" t="n"/>
+      <c r="T240" s="7" t="n"/>
+      <c r="U240" s="8" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V240" s="8" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W240" s="8" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X240" s="8" t="inlineStr">
         <is>
           <t>17 de agosto de 2026</t>
         </is>
@@ -16417,7 +16483,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fuente: INEGI · Periodo: Jun 26 · Nota: variaciones anuales en cifras originales.</t>
+          <t>Fuente: INEGI · Periodo: Jul 26 · Nota: variaciones anuales en cifras originales.</t>
         </is>
       </c>
     </row>

--- a/downloads/indicadores/EMIM/EMIM_datos.xlsx
+++ b/downloads/indicadores/EMIM/EMIM_datos.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X240"/>
+  <dimension ref="A1:X241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14874,13 +14874,13 @@
         <v>45658</v>
       </c>
       <c r="C222" s="6" t="n">
-        <v>107.4</v>
+        <v>107.1</v>
       </c>
       <c r="D222" s="7" t="n">
-        <v>0.082661</v>
+        <v>0.079637</v>
       </c>
       <c r="E222" s="7" t="n">
-        <v>-0.012868</v>
+        <v>-0.015625</v>
       </c>
       <c r="F222" s="7" t="n">
         <v>-0.004</v>
@@ -14889,13 +14889,13 @@
         <v>-0.019</v>
       </c>
       <c r="H222" s="6" t="n">
-        <v>100.4</v>
+        <v>100.5</v>
       </c>
       <c r="I222" s="7" t="n">
-        <v>0.0009970000000000001</v>
+        <v>0.001994</v>
       </c>
       <c r="J222" s="7" t="n">
-        <v>-0.009861999999999999</v>
+        <v>-0.008876</v>
       </c>
       <c r="K222" s="7" t="n">
         <v>0.002</v>
@@ -14958,13 +14958,13 @@
         <v>45689</v>
       </c>
       <c r="C223" s="9" t="n">
-        <v>106</v>
+        <v>105.9</v>
       </c>
       <c r="D223" s="10" t="n">
-        <v>-0.013035</v>
+        <v>-0.011204</v>
       </c>
       <c r="E223" s="10" t="n">
-        <v>-0.013953</v>
+        <v>-0.014884</v>
       </c>
       <c r="F223" s="10" t="n">
         <v>0.026</v>
@@ -14973,13 +14973,13 @@
         <v>0.014</v>
       </c>
       <c r="H223" s="9" t="n">
-        <v>100.4</v>
+        <v>100.5</v>
       </c>
       <c r="I223" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J223" s="10" t="n">
-        <v>-0.011811</v>
+        <v>-0.010827</v>
       </c>
       <c r="K223" s="10" t="n">
         <v>-0.003</v>
@@ -15042,13 +15042,13 @@
         <v>45717</v>
       </c>
       <c r="C224" s="6" t="n">
-        <v>113.5</v>
+        <v>113.4</v>
       </c>
       <c r="D224" s="7" t="n">
-        <v>0.070755</v>
+        <v>0.070822</v>
       </c>
       <c r="E224" s="7" t="n">
-        <v>0.020683</v>
+        <v>0.019784</v>
       </c>
       <c r="F224" s="7" t="n">
         <v>-0.02</v>
@@ -15060,7 +15060,7 @@
         <v>100.5</v>
       </c>
       <c r="I224" s="7" t="n">
-        <v>0.0009959999999999999</v>
+        <v>0</v>
       </c>
       <c r="J224" s="7" t="n">
         <v>-0.008876</v>
@@ -15072,13 +15072,13 @@
         <v>-0.008</v>
       </c>
       <c r="M224" s="6" t="n">
-        <v>98.3</v>
+        <v>98.2</v>
       </c>
       <c r="N224" s="7" t="n">
-        <v>0.053591</v>
+        <v>0.052519</v>
       </c>
       <c r="O224" s="7" t="n">
-        <v>0.007172</v>
+        <v>0.006148</v>
       </c>
       <c r="P224" s="7" t="n">
         <v>-0.007</v>
@@ -15126,13 +15126,13 @@
         <v>45748</v>
       </c>
       <c r="C225" s="9" t="n">
-        <v>108.9</v>
+        <v>109</v>
       </c>
       <c r="D225" s="10" t="n">
-        <v>-0.040529</v>
+        <v>-0.038801</v>
       </c>
       <c r="E225" s="10" t="n">
-        <v>-0.037986</v>
+        <v>-0.037102</v>
       </c>
       <c r="F225" s="10" t="n">
         <v>-0.001</v>
@@ -15156,13 +15156,13 @@
         <v>-0.016</v>
       </c>
       <c r="M225" s="9" t="n">
-        <v>97.40000000000001</v>
+        <v>97.3</v>
       </c>
       <c r="N225" s="10" t="n">
-        <v>-0.009155999999999999</v>
+        <v>-0.009165</v>
       </c>
       <c r="O225" s="10" t="n">
-        <v>-0.032771</v>
+        <v>-0.033764</v>
       </c>
       <c r="P225" s="10" t="n">
         <v>0.005</v>
@@ -15213,7 +15213,7 @@
         <v>112.1</v>
       </c>
       <c r="D226" s="7" t="n">
-        <v>0.029385</v>
+        <v>0.02844</v>
       </c>
       <c r="E226" s="7" t="n">
         <v>0.005381</v>
@@ -15243,7 +15243,7 @@
         <v>99.90000000000001</v>
       </c>
       <c r="N226" s="7" t="n">
-        <v>0.025667</v>
+        <v>0.026721</v>
       </c>
       <c r="O226" s="7" t="n">
         <v>-0.032914</v>
@@ -15294,13 +15294,13 @@
         <v>45809</v>
       </c>
       <c r="C227" s="9" t="n">
-        <v>111.9</v>
+        <v>112</v>
       </c>
       <c r="D227" s="10" t="n">
-        <v>-0.001784</v>
+        <v>-0.000892</v>
       </c>
       <c r="E227" s="10" t="n">
-        <v>0.031336</v>
+        <v>0.032258</v>
       </c>
       <c r="F227" s="10" t="n">
         <v>0.016</v>
@@ -15309,13 +15309,13 @@
         <v>0.023</v>
       </c>
       <c r="H227" s="9" t="n">
-        <v>100.1</v>
+        <v>100</v>
       </c>
       <c r="I227" s="10" t="n">
-        <v>-0.002988</v>
+        <v>-0.003984</v>
       </c>
       <c r="J227" s="10" t="n">
-        <v>-0.019589</v>
+        <v>-0.020568</v>
       </c>
       <c r="K227" s="10" t="n">
         <v>-0.002</v>
@@ -15324,13 +15324,13 @@
         <v>-0.02</v>
       </c>
       <c r="M227" s="9" t="n">
-        <v>97.90000000000001</v>
+        <v>97.8</v>
       </c>
       <c r="N227" s="10" t="n">
-        <v>-0.02002</v>
+        <v>-0.021021</v>
       </c>
       <c r="O227" s="10" t="n">
-        <v>-0.013105</v>
+        <v>-0.014113</v>
       </c>
       <c r="P227" s="10" t="n">
         <v>0</v>
@@ -15378,13 +15378,13 @@
         <v>45839</v>
       </c>
       <c r="C228" s="6" t="n">
-        <v>110.2</v>
+        <v>110.3</v>
       </c>
       <c r="D228" s="7" t="n">
-        <v>-0.015192</v>
+        <v>-0.015179</v>
       </c>
       <c r="E228" s="7" t="n">
-        <v>-0.000907</v>
+        <v>0</v>
       </c>
       <c r="F228" s="7" t="n">
         <v>-0.027</v>
@@ -15396,7 +15396,7 @@
         <v>99.7</v>
       </c>
       <c r="I228" s="7" t="n">
-        <v>-0.003996</v>
+        <v>-0.003</v>
       </c>
       <c r="J228" s="7" t="n">
         <v>-0.022549</v>
@@ -15411,7 +15411,7 @@
         <v>101.4</v>
       </c>
       <c r="N228" s="7" t="n">
-        <v>0.035751</v>
+        <v>0.03681</v>
       </c>
       <c r="O228" s="7" t="n">
         <v>-0.010732</v>
@@ -15462,13 +15462,13 @@
         <v>45870</v>
       </c>
       <c r="C229" s="9" t="n">
-        <v>109.4</v>
+        <v>109.3</v>
       </c>
       <c r="D229" s="10" t="n">
-        <v>-0.00726</v>
+        <v>-0.009065999999999999</v>
       </c>
       <c r="E229" s="10" t="n">
-        <v>-0.030142</v>
+        <v>-0.031028</v>
       </c>
       <c r="F229" s="10" t="n">
         <v>-0.003</v>
@@ -15492,13 +15492,13 @@
         <v>-0.027</v>
       </c>
       <c r="M229" s="9" t="n">
-        <v>98.59999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="N229" s="10" t="n">
-        <v>-0.027613</v>
+        <v>-0.0286</v>
       </c>
       <c r="O229" s="10" t="n">
-        <v>-0.052834</v>
+        <v>-0.053794</v>
       </c>
       <c r="P229" s="10" t="n">
         <v>-0.006</v>
@@ -15546,13 +15546,13 @@
         <v>45901</v>
       </c>
       <c r="C230" s="6" t="n">
-        <v>109.1</v>
+        <v>109</v>
       </c>
       <c r="D230" s="7" t="n">
-        <v>-0.002742</v>
+        <v>-0.002745</v>
       </c>
       <c r="E230" s="7" t="n">
-        <v>-0.007279</v>
+        <v>-0.008189</v>
       </c>
       <c r="F230" s="7" t="n">
         <v>0.002</v>
@@ -15576,13 +15576,13 @@
         <v>-0.026</v>
       </c>
       <c r="M230" s="6" t="n">
-        <v>96.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="N230" s="7" t="n">
-        <v>-0.017241</v>
+        <v>-0.017259</v>
       </c>
       <c r="O230" s="7" t="n">
-        <v>-0.018237</v>
+        <v>-0.01925</v>
       </c>
       <c r="P230" s="7" t="n">
         <v>-0.004</v>
@@ -15633,7 +15633,7 @@
         <v>112.9</v>
       </c>
       <c r="D231" s="10" t="n">
-        <v>0.03483</v>
+        <v>0.03578</v>
       </c>
       <c r="E231" s="10" t="n">
         <v>0.008036</v>
@@ -15660,13 +15660,13 @@
         <v>-0.025</v>
       </c>
       <c r="M231" s="9" t="n">
-        <v>102.4</v>
+        <v>102.3</v>
       </c>
       <c r="N231" s="10" t="n">
-        <v>0.05676</v>
+        <v>0.056818</v>
       </c>
       <c r="O231" s="10" t="n">
-        <v>-0.014437</v>
+        <v>-0.015399</v>
       </c>
       <c r="P231" s="10" t="n">
         <v>0.006</v>
@@ -15714,13 +15714,13 @@
         <v>45962</v>
       </c>
       <c r="C232" s="6" t="n">
-        <v>107.8</v>
+        <v>108.2</v>
       </c>
       <c r="D232" s="7" t="n">
-        <v>-0.045173</v>
+        <v>-0.04163</v>
       </c>
       <c r="E232" s="7" t="n">
-        <v>0.000929</v>
+        <v>0.004643</v>
       </c>
       <c r="F232" s="7" t="n">
         <v>0.01</v>
@@ -15729,13 +15729,13 @@
         <v>0.014</v>
       </c>
       <c r="H232" s="6" t="n">
-        <v>98.3</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I232" s="7" t="n">
-        <v>-0.007071</v>
+        <v>-0.006061</v>
       </c>
       <c r="J232" s="7" t="n">
-        <v>-0.027695</v>
+        <v>-0.026706</v>
       </c>
       <c r="K232" s="7" t="n">
         <v>-0.004</v>
@@ -15747,7 +15747,7 @@
         <v>94.2</v>
       </c>
       <c r="N232" s="7" t="n">
-        <v>-0.080078</v>
+        <v>-0.079179</v>
       </c>
       <c r="O232" s="7" t="n">
         <v>-0.045593</v>
@@ -15798,13 +15798,13 @@
         <v>45992</v>
       </c>
       <c r="C233" s="9" t="n">
-        <v>103.5</v>
+        <v>103.7</v>
       </c>
       <c r="D233" s="10" t="n">
-        <v>-0.039889</v>
+        <v>-0.04159</v>
       </c>
       <c r="E233" s="10" t="n">
-        <v>0.043347</v>
+        <v>0.045363</v>
       </c>
       <c r="F233" s="10" t="n">
         <v>-0.001</v>
@@ -15813,13 +15813,13 @@
         <v>0.029</v>
       </c>
       <c r="H233" s="9" t="n">
-        <v>97.7</v>
+        <v>97.8</v>
       </c>
       <c r="I233" s="10" t="n">
-        <v>-0.006104</v>
+        <v>-0.006098</v>
       </c>
       <c r="J233" s="10" t="n">
-        <v>-0.025922</v>
+        <v>-0.024925</v>
       </c>
       <c r="K233" s="10" t="n">
         <v>0</v>
@@ -15828,13 +15828,13 @@
         <v>-0.026</v>
       </c>
       <c r="M233" s="9" t="n">
-        <v>91.3</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="N233" s="10" t="n">
-        <v>-0.030786</v>
+        <v>-0.029724</v>
       </c>
       <c r="O233" s="10" t="n">
-        <v>-0.009761000000000001</v>
+        <v>-0.008677000000000001</v>
       </c>
       <c r="P233" s="10" t="n">
         <v>-0.001</v>
@@ -15882,13 +15882,13 @@
         <v>46023</v>
       </c>
       <c r="C234" s="6" t="n">
-        <v>105.8</v>
+        <v>105.9</v>
       </c>
       <c r="D234" s="7" t="n">
-        <v>0.022222</v>
+        <v>0.021215</v>
       </c>
       <c r="E234" s="7" t="n">
-        <v>-0.014898</v>
+        <v>-0.011204</v>
       </c>
       <c r="F234" s="7" t="n">
         <v>-0.018</v>
@@ -15900,10 +15900,10 @@
         <v>97.90000000000001</v>
       </c>
       <c r="I234" s="7" t="n">
-        <v>0.002047</v>
+        <v>0.001022</v>
       </c>
       <c r="J234" s="7" t="n">
-        <v>-0.0249</v>
+        <v>-0.025871</v>
       </c>
       <c r="K234" s="7" t="n">
         <v>0.002</v>
@@ -15915,7 +15915,7 @@
         <v>95.7</v>
       </c>
       <c r="N234" s="7" t="n">
-        <v>0.048193</v>
+        <v>0.047046</v>
       </c>
       <c r="O234" s="7" t="n">
         <v>-0.034309</v>
@@ -15966,13 +15966,13 @@
         <v>46054</v>
       </c>
       <c r="C235" s="9" t="n">
-        <v>107.1</v>
+        <v>107</v>
       </c>
       <c r="D235" s="10" t="n">
-        <v>0.012287</v>
+        <v>0.010387</v>
       </c>
       <c r="E235" s="10" t="n">
-        <v>0.010377</v>
+        <v>0.010387</v>
       </c>
       <c r="F235" s="10" t="n">
         <v>0.034</v>
@@ -15981,13 +15981,13 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="H235" s="9" t="n">
-        <v>97.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I235" s="10" t="n">
-        <v>-0.001021</v>
+        <v>-0.003064</v>
       </c>
       <c r="J235" s="10" t="n">
-        <v>-0.025896</v>
+        <v>-0.028856</v>
       </c>
       <c r="K235" s="10" t="n">
         <v>-0.003</v>
@@ -15996,13 +15996,13 @@
         <v>-0.026</v>
       </c>
       <c r="M235" s="9" t="n">
-        <v>90.40000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="N235" s="10" t="n">
-        <v>-0.055381</v>
+        <v>-0.057471</v>
       </c>
       <c r="O235" s="10" t="n">
-        <v>-0.031083</v>
+        <v>-0.033226</v>
       </c>
       <c r="P235" s="10" t="n">
         <v>0.002</v>
@@ -16050,13 +16050,13 @@
         <v>46082</v>
       </c>
       <c r="C236" s="6" t="n">
-        <v>115.4</v>
+        <v>115.5</v>
       </c>
       <c r="D236" s="7" t="n">
-        <v>0.077498</v>
+        <v>0.079439</v>
       </c>
       <c r="E236" s="7" t="n">
-        <v>0.01674</v>
+        <v>0.018519</v>
       </c>
       <c r="F236" s="7" t="n">
         <v>-0.011</v>
@@ -16065,13 +16065,13 @@
         <v>0.011</v>
       </c>
       <c r="H236" s="6" t="n">
-        <v>98</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="I236" s="7" t="n">
-        <v>0.002045</v>
+        <v>0.003074</v>
       </c>
       <c r="J236" s="7" t="n">
-        <v>-0.024876</v>
+        <v>-0.025871</v>
       </c>
       <c r="K236" s="7" t="n">
         <v>-0.001</v>
@@ -16083,10 +16083,10 @@
         <v>96.59999999999999</v>
       </c>
       <c r="N236" s="7" t="n">
-        <v>0.06858400000000001</v>
+        <v>0.070953</v>
       </c>
       <c r="O236" s="7" t="n">
-        <v>-0.017294</v>
+        <v>-0.016293</v>
       </c>
       <c r="P236" s="7" t="n">
         <v>0</v>
@@ -16134,13 +16134,13 @@
         <v>46113</v>
       </c>
       <c r="C237" s="9" t="n">
-        <v>111.2</v>
+        <v>111.4</v>
       </c>
       <c r="D237" s="10" t="n">
-        <v>-0.036395</v>
+        <v>-0.035498</v>
       </c>
       <c r="E237" s="10" t="n">
-        <v>0.02112</v>
+        <v>0.022018</v>
       </c>
       <c r="F237" s="10" t="n">
         <v>0.005</v>
@@ -16149,13 +16149,13 @@
         <v>0.019</v>
       </c>
       <c r="H237" s="9" t="n">
-        <v>98.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="I237" s="10" t="n">
-        <v>0.00102</v>
+        <v>0.003064</v>
       </c>
       <c r="J237" s="10" t="n">
-        <v>-0.023881</v>
+        <v>-0.022886</v>
       </c>
       <c r="K237" s="10" t="n">
         <v>-0.002</v>
@@ -16164,13 +16164,13 @@
         <v>-0.024</v>
       </c>
       <c r="M237" s="9" t="n">
-        <v>96.59999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="N237" s="10" t="n">
-        <v>0</v>
+        <v>0.001035</v>
       </c>
       <c r="O237" s="10" t="n">
-        <v>-0.008214000000000001</v>
+        <v>-0.006166</v>
       </c>
       <c r="P237" s="10" t="n">
         <v>0.006</v>
@@ -16221,7 +16221,7 @@
         <v>110.4</v>
       </c>
       <c r="D238" s="7" t="n">
-        <v>-0.007194</v>
+        <v>-0.008977000000000001</v>
       </c>
       <c r="E238" s="7" t="n">
         <v>-0.015165</v>
@@ -16233,13 +16233,13 @@
         <v>-0.001</v>
       </c>
       <c r="H238" s="6" t="n">
-        <v>98.3</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I238" s="7" t="n">
-        <v>0.002039</v>
+        <v>0.002037</v>
       </c>
       <c r="J238" s="7" t="n">
-        <v>-0.020916</v>
+        <v>-0.01992</v>
       </c>
       <c r="K238" s="7" t="n">
         <v>-0.001</v>
@@ -16248,13 +16248,13 @@
         <v>-0.021</v>
       </c>
       <c r="M238" s="6" t="n">
-        <v>96</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="N238" s="7" t="n">
-        <v>-0.006211</v>
+        <v>-0.006205</v>
       </c>
       <c r="O238" s="7" t="n">
-        <v>-0.039039</v>
+        <v>-0.038038</v>
       </c>
       <c r="P238" s="7" t="n">
         <v>-0.005</v>
@@ -16302,13 +16302,13 @@
         <v>46174</v>
       </c>
       <c r="C239" s="9" t="n">
-        <v>110.7</v>
+        <v>110.8</v>
       </c>
       <c r="D239" s="10" t="n">
-        <v>0.002717</v>
+        <v>0.003623</v>
       </c>
       <c r="E239" s="10" t="n">
-        <v>-0.010724</v>
+        <v>-0.010714</v>
       </c>
       <c r="F239" s="10" t="n">
         <v>0.001</v>
@@ -16317,13 +16317,13 @@
         <v>-0.024</v>
       </c>
       <c r="H239" s="9" t="n">
-        <v>98.59999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="I239" s="10" t="n">
-        <v>0.003052</v>
+        <v>0.001016</v>
       </c>
       <c r="J239" s="10" t="n">
-        <v>-0.014985</v>
+        <v>-0.015</v>
       </c>
       <c r="K239" s="10" t="n">
         <v>0.001</v>
@@ -16335,10 +16335,10 @@
         <v>97.8</v>
       </c>
       <c r="N239" s="10" t="n">
-        <v>0.01875</v>
+        <v>0.01769</v>
       </c>
       <c r="O239" s="10" t="n">
-        <v>-0.001021</v>
+        <v>0</v>
       </c>
       <c r="P239" s="10" t="n">
         <v>0.001</v>
@@ -16389,10 +16389,10 @@
         <v>112.2</v>
       </c>
       <c r="D240" s="7" t="n">
-        <v>0.01355</v>
+        <v>0.012635</v>
       </c>
       <c r="E240" s="7" t="n">
-        <v>0.018149</v>
+        <v>0.017226</v>
       </c>
       <c r="F240" s="7" t="n"/>
       <c r="G240" s="7" t="n"/>
@@ -16400,7 +16400,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="I240" s="7" t="n">
-        <v>-0.002028</v>
+        <v>-0.001015</v>
       </c>
       <c r="J240" s="7" t="n">
         <v>-0.013039</v>
@@ -16437,6 +16437,72 @@
         </is>
       </c>
       <c r="X240" s="8" t="inlineStr">
+        <is>
+          <t>17 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="4" t="inlineStr">
+        <is>
+          <t>Ago 26</t>
+        </is>
+      </c>
+      <c r="B241" s="5" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C241" s="9" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="D241" s="10" t="n">
+        <v>0.013369</v>
+      </c>
+      <c r="E241" s="10" t="n">
+        <v>0.040256</v>
+      </c>
+      <c r="F241" s="10" t="n"/>
+      <c r="G241" s="10" t="n"/>
+      <c r="H241" s="9" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="I241" s="10" t="n">
+        <v>-0.002033</v>
+      </c>
+      <c r="J241" s="10" t="n">
+        <v>-0.010081</v>
+      </c>
+      <c r="K241" s="10" t="n"/>
+      <c r="L241" s="10" t="n"/>
+      <c r="M241" s="9" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="N241" s="10" t="n">
+        <v>-0.029851</v>
+      </c>
+      <c r="O241" s="10" t="n">
+        <v>-0.010152</v>
+      </c>
+      <c r="P241" s="10" t="n"/>
+      <c r="Q241" s="10" t="n"/>
+      <c r="R241" s="9" t="n"/>
+      <c r="S241" s="10" t="n"/>
+      <c r="T241" s="10" t="n"/>
+      <c r="U241" s="11" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="V241" s="11" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="W241" s="11" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="X241" s="11" t="inlineStr">
         <is>
           <t>17 de agosto de 2026</t>
         </is>
@@ -16483,7 +16549,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fuente: INEGI · Periodo: Jul 26 · Nota: variaciones anuales en cifras originales.</t>
+          <t>Fuente: INEGI · Periodo: Ago 26 · Nota: variaciones anuales en cifras originales.</t>
         </is>
       </c>
     </row>

--- a/downloads/indicadores/EMIM/EMIM_datos.xlsx
+++ b/downloads/indicadores/EMIM/EMIM_datos.xlsx
@@ -524,7 +524,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf · Fecha de publicación: 17 de agosto de 2026</t>
+          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf · Fecha de publicación: 16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -695,12 +695,12 @@
       </c>
       <c r="W6" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X6" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -755,12 +755,12 @@
       </c>
       <c r="W7" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X7" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -815,12 +815,12 @@
       </c>
       <c r="W8" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X8" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="W9" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X9" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="W10" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X10" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="W11" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X11" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="W12" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X12" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1115,12 +1115,12 @@
       </c>
       <c r="W13" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X13" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="W14" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X14" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="W15" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X15" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="W16" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X16" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="W17" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X17" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1421,12 +1421,12 @@
       </c>
       <c r="W18" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X18" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1487,12 +1487,12 @@
       </c>
       <c r="W19" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X19" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1553,12 +1553,12 @@
       </c>
       <c r="W20" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X20" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="W21" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X21" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1685,12 +1685,12 @@
       </c>
       <c r="W22" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X22" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="W23" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X23" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1817,12 +1817,12 @@
       </c>
       <c r="W24" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X24" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1883,12 +1883,12 @@
       </c>
       <c r="W25" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X25" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1949,12 +1949,12 @@
       </c>
       <c r="W26" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X26" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="W27" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X27" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2081,12 +2081,12 @@
       </c>
       <c r="W28" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X28" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2147,12 +2147,12 @@
       </c>
       <c r="W29" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X29" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="W30" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X30" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2279,12 +2279,12 @@
       </c>
       <c r="W31" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X31" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2345,12 +2345,12 @@
       </c>
       <c r="W32" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X32" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2411,12 +2411,12 @@
       </c>
       <c r="W33" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X33" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2477,12 +2477,12 @@
       </c>
       <c r="W34" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X34" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2543,12 +2543,12 @@
       </c>
       <c r="W35" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X35" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="W36" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X36" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2675,12 +2675,12 @@
       </c>
       <c r="W37" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X37" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2741,12 +2741,12 @@
       </c>
       <c r="W38" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X38" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2807,12 +2807,12 @@
       </c>
       <c r="W39" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X39" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2873,12 +2873,12 @@
       </c>
       <c r="W40" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X40" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2939,12 +2939,12 @@
       </c>
       <c r="W41" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X41" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="W42" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X42" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3071,12 +3071,12 @@
       </c>
       <c r="W43" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X43" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3137,12 +3137,12 @@
       </c>
       <c r="W44" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X44" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3203,12 +3203,12 @@
       </c>
       <c r="W45" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X45" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3269,12 +3269,12 @@
       </c>
       <c r="W46" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X46" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3335,12 +3335,12 @@
       </c>
       <c r="W47" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X47" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3401,12 +3401,12 @@
       </c>
       <c r="W48" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X48" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3467,12 +3467,12 @@
       </c>
       <c r="W49" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X49" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3533,12 +3533,12 @@
       </c>
       <c r="W50" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X50" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3599,12 +3599,12 @@
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X51" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3665,12 +3665,12 @@
       </c>
       <c r="W52" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X52" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3731,12 +3731,12 @@
       </c>
       <c r="W53" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X53" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="W54" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X54" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="W55" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X55" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3929,12 +3929,12 @@
       </c>
       <c r="W56" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X56" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3995,12 +3995,12 @@
       </c>
       <c r="W57" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X57" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4061,12 +4061,12 @@
       </c>
       <c r="W58" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X58" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4127,12 +4127,12 @@
       </c>
       <c r="W59" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X59" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4193,12 +4193,12 @@
       </c>
       <c r="W60" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X60" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="W61" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X61" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4325,12 +4325,12 @@
       </c>
       <c r="W62" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X62" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4391,12 +4391,12 @@
       </c>
       <c r="W63" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X63" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4457,12 +4457,12 @@
       </c>
       <c r="W64" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X64" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4523,12 +4523,12 @@
       </c>
       <c r="W65" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X65" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4589,12 +4589,12 @@
       </c>
       <c r="W66" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X66" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4655,12 +4655,12 @@
       </c>
       <c r="W67" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X67" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4721,12 +4721,12 @@
       </c>
       <c r="W68" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X68" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4787,12 +4787,12 @@
       </c>
       <c r="W69" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X69" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="W70" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X70" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4919,12 +4919,12 @@
       </c>
       <c r="W71" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X71" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4985,12 +4985,12 @@
       </c>
       <c r="W72" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X72" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5051,12 +5051,12 @@
       </c>
       <c r="W73" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X73" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5117,12 +5117,12 @@
       </c>
       <c r="W74" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X74" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="W75" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X75" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5249,12 +5249,12 @@
       </c>
       <c r="W76" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X76" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5315,12 +5315,12 @@
       </c>
       <c r="W77" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X77" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5381,12 +5381,12 @@
       </c>
       <c r="W78" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X78" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5447,12 +5447,12 @@
       </c>
       <c r="W79" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X79" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5513,12 +5513,12 @@
       </c>
       <c r="W80" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X80" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5579,12 +5579,12 @@
       </c>
       <c r="W81" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X81" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5645,12 +5645,12 @@
       </c>
       <c r="W82" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X82" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5711,12 +5711,12 @@
       </c>
       <c r="W83" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X83" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5777,12 +5777,12 @@
       </c>
       <c r="W84" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X84" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="W85" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X85" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5909,12 +5909,12 @@
       </c>
       <c r="W86" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X86" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5975,12 +5975,12 @@
       </c>
       <c r="W87" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X87" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6041,12 +6041,12 @@
       </c>
       <c r="W88" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X88" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="W89" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X89" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6173,12 @@
       </c>
       <c r="W90" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X90" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6239,12 +6239,12 @@
       </c>
       <c r="W91" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X91" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6305,12 +6305,12 @@
       </c>
       <c r="W92" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X92" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6371,12 +6371,12 @@
       </c>
       <c r="W93" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X93" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="W94" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X94" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6503,12 +6503,12 @@
       </c>
       <c r="W95" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X95" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="W96" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X96" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6635,12 +6635,12 @@
       </c>
       <c r="W97" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X97" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6701,12 +6701,12 @@
       </c>
       <c r="W98" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X98" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6767,12 +6767,12 @@
       </c>
       <c r="W99" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X99" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6833,12 +6833,12 @@
       </c>
       <c r="W100" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X100" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6899,12 +6899,12 @@
       </c>
       <c r="W101" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X101" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6965,12 +6965,12 @@
       </c>
       <c r="W102" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X102" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="W103" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X103" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7097,12 +7097,12 @@
       </c>
       <c r="W104" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X104" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7163,12 +7163,12 @@
       </c>
       <c r="W105" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X105" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7229,12 +7229,12 @@
       </c>
       <c r="W106" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X106" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7295,12 +7295,12 @@
       </c>
       <c r="W107" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X107" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7361,12 +7361,12 @@
       </c>
       <c r="W108" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X108" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7427,12 +7427,12 @@
       </c>
       <c r="W109" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X109" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7493,12 +7493,12 @@
       </c>
       <c r="W110" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X110" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="W111" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X111" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7625,12 +7625,12 @@
       </c>
       <c r="W112" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X112" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7691,12 +7691,12 @@
       </c>
       <c r="W113" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X113" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7757,12 +7757,12 @@
       </c>
       <c r="W114" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X114" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7823,12 +7823,12 @@
       </c>
       <c r="W115" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X115" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7889,12 +7889,12 @@
       </c>
       <c r="W116" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X116" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7955,12 +7955,12 @@
       </c>
       <c r="W117" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X117" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8021,12 +8021,12 @@
       </c>
       <c r="W118" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X118" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8087,12 +8087,12 @@
       </c>
       <c r="W119" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X119" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8153,12 +8153,12 @@
       </c>
       <c r="W120" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X120" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8219,12 +8219,12 @@
       </c>
       <c r="W121" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X121" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8285,12 +8285,12 @@
       </c>
       <c r="W122" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X122" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8351,12 +8351,12 @@
       </c>
       <c r="W123" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X123" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8417,12 +8417,12 @@
       </c>
       <c r="W124" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X124" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8483,12 +8483,12 @@
       </c>
       <c r="W125" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X125" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8549,12 +8549,12 @@
       </c>
       <c r="W126" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X126" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8615,12 +8615,12 @@
       </c>
       <c r="W127" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X127" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8681,12 +8681,12 @@
       </c>
       <c r="W128" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X128" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8747,12 +8747,12 @@
       </c>
       <c r="W129" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X129" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8813,12 +8813,12 @@
       </c>
       <c r="W130" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X130" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8879,12 +8879,12 @@
       </c>
       <c r="W131" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X131" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8945,12 +8945,12 @@
       </c>
       <c r="W132" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X132" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9011,12 +9011,12 @@
       </c>
       <c r="W133" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X133" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9077,12 +9077,12 @@
       </c>
       <c r="W134" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X134" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9143,12 +9143,12 @@
       </c>
       <c r="W135" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X135" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9209,12 +9209,12 @@
       </c>
       <c r="W136" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X136" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9275,12 +9275,12 @@
       </c>
       <c r="W137" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X137" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9341,12 +9341,12 @@
       </c>
       <c r="W138" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X138" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="W139" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X139" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9473,12 +9473,12 @@
       </c>
       <c r="W140" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X140" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9539,12 +9539,12 @@
       </c>
       <c r="W141" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X141" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9605,12 +9605,12 @@
       </c>
       <c r="W142" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X142" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9671,12 +9671,12 @@
       </c>
       <c r="W143" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X143" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9737,12 +9737,12 @@
       </c>
       <c r="W144" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X144" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9803,12 +9803,12 @@
       </c>
       <c r="W145" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X145" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="W146" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X146" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -9935,12 +9935,12 @@
       </c>
       <c r="W147" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X147" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10001,12 +10001,12 @@
       </c>
       <c r="W148" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X148" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10067,12 +10067,12 @@
       </c>
       <c r="W149" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X149" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10133,12 +10133,12 @@
       </c>
       <c r="W150" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X150" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10199,12 +10199,12 @@
       </c>
       <c r="W151" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X151" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10265,12 +10265,12 @@
       </c>
       <c r="W152" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X152" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10331,12 +10331,12 @@
       </c>
       <c r="W153" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X153" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10397,12 +10397,12 @@
       </c>
       <c r="W154" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X154" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10463,12 +10463,12 @@
       </c>
       <c r="W155" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X155" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10529,12 +10529,12 @@
       </c>
       <c r="W156" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X156" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10595,12 +10595,12 @@
       </c>
       <c r="W157" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X157" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10661,12 +10661,12 @@
       </c>
       <c r="W158" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X158" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10727,12 +10727,12 @@
       </c>
       <c r="W159" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X159" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10793,12 +10793,12 @@
       </c>
       <c r="W160" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X160" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10859,12 +10859,12 @@
       </c>
       <c r="W161" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X161" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10925,12 +10925,12 @@
       </c>
       <c r="W162" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X162" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10991,12 +10991,12 @@
       </c>
       <c r="W163" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X163" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11057,12 +11057,12 @@
       </c>
       <c r="W164" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X164" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11123,12 +11123,12 @@
       </c>
       <c r="W165" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X165" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11189,12 +11189,12 @@
       </c>
       <c r="W166" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X166" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11255,12 +11255,12 @@
       </c>
       <c r="W167" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X167" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11321,12 +11321,12 @@
       </c>
       <c r="W168" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X168" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11387,12 +11387,12 @@
       </c>
       <c r="W169" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X169" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11453,12 +11453,12 @@
       </c>
       <c r="W170" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X170" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11519,12 +11519,12 @@
       </c>
       <c r="W171" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X171" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11585,12 +11585,12 @@
       </c>
       <c r="W172" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X172" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11651,12 +11651,12 @@
       </c>
       <c r="W173" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X173" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11717,12 +11717,12 @@
       </c>
       <c r="W174" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X174" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11783,12 +11783,12 @@
       </c>
       <c r="W175" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X175" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11849,12 +11849,12 @@
       </c>
       <c r="W176" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X176" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11915,12 +11915,12 @@
       </c>
       <c r="W177" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X177" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -11981,12 +11981,12 @@
       </c>
       <c r="W178" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X178" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12047,12 +12047,12 @@
       </c>
       <c r="W179" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X179" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12113,12 +12113,12 @@
       </c>
       <c r="W180" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X180" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12179,12 +12179,12 @@
       </c>
       <c r="W181" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X181" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12245,12 +12245,12 @@
       </c>
       <c r="W182" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X182" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12311,12 +12311,12 @@
       </c>
       <c r="W183" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X183" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12377,12 +12377,12 @@
       </c>
       <c r="W184" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X184" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12443,12 +12443,12 @@
       </c>
       <c r="W185" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X185" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12509,12 +12509,12 @@
       </c>
       <c r="W186" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X186" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12575,12 +12575,12 @@
       </c>
       <c r="W187" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X187" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12641,12 +12641,12 @@
       </c>
       <c r="W188" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X188" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12707,12 +12707,12 @@
       </c>
       <c r="W189" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X189" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12773,12 +12773,12 @@
       </c>
       <c r="W190" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X190" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12839,12 +12839,12 @@
       </c>
       <c r="W191" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X191" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12905,12 +12905,12 @@
       </c>
       <c r="W192" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X192" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -12971,12 +12971,12 @@
       </c>
       <c r="W193" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X193" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13037,12 +13037,12 @@
       </c>
       <c r="W194" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X194" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="W195" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X195" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13169,12 +13169,12 @@
       </c>
       <c r="W196" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X196" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13235,12 +13235,12 @@
       </c>
       <c r="W197" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X197" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13301,12 +13301,12 @@
       </c>
       <c r="W198" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X198" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13367,12 +13367,12 @@
       </c>
       <c r="W199" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X199" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13433,12 +13433,12 @@
       </c>
       <c r="W200" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X200" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13499,12 +13499,12 @@
       </c>
       <c r="W201" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X201" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13565,12 +13565,12 @@
       </c>
       <c r="W202" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X202" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13631,12 +13631,12 @@
       </c>
       <c r="W203" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X203" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13697,12 +13697,12 @@
       </c>
       <c r="W204" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X204" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13763,12 +13763,12 @@
       </c>
       <c r="W205" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X205" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13829,12 +13829,12 @@
       </c>
       <c r="W206" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X206" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13895,12 +13895,12 @@
       </c>
       <c r="W207" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X207" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -13961,12 +13961,12 @@
       </c>
       <c r="W208" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X208" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14027,12 +14027,12 @@
       </c>
       <c r="W209" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X209" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14093,12 +14093,12 @@
       </c>
       <c r="W210" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X210" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="W211" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X211" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14225,12 +14225,12 @@
       </c>
       <c r="W212" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X212" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14291,12 +14291,12 @@
       </c>
       <c r="W213" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X213" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14357,12 +14357,12 @@
       </c>
       <c r="W214" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X214" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14423,12 +14423,12 @@
       </c>
       <c r="W215" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X215" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14489,12 +14489,12 @@
       </c>
       <c r="W216" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X216" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14555,12 +14555,12 @@
       </c>
       <c r="W217" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X217" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="W218" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X218" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14687,12 +14687,12 @@
       </c>
       <c r="W219" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X219" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14771,12 +14771,12 @@
       </c>
       <c r="W220" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X220" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14855,12 +14855,12 @@
       </c>
       <c r="W221" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X221" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -14939,12 +14939,12 @@
       </c>
       <c r="W222" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X222" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -15023,12 +15023,12 @@
       </c>
       <c r="W223" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X223" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -15107,12 +15107,12 @@
       </c>
       <c r="W224" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X224" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -15191,12 +15191,12 @@
       </c>
       <c r="W225" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X225" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -15275,12 +15275,12 @@
       </c>
       <c r="W226" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X226" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -15359,12 +15359,12 @@
       </c>
       <c r="W227" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X227" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -15443,12 +15443,12 @@
       </c>
       <c r="W228" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X228" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -15527,12 +15527,12 @@
       </c>
       <c r="W229" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X229" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -15611,12 +15611,12 @@
       </c>
       <c r="W230" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X230" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -15695,12 +15695,12 @@
       </c>
       <c r="W231" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X231" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -15779,12 +15779,12 @@
       </c>
       <c r="W232" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X232" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -15863,12 +15863,12 @@
       </c>
       <c r="W233" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X233" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -15947,12 +15947,12 @@
       </c>
       <c r="W234" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X234" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -16031,12 +16031,12 @@
       </c>
       <c r="W235" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X235" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -16115,12 +16115,12 @@
       </c>
       <c r="W236" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X236" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -16199,12 +16199,12 @@
       </c>
       <c r="W237" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X237" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -16283,12 +16283,12 @@
       </c>
       <c r="W238" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X238" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -16367,12 +16367,12 @@
       </c>
       <c r="W239" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X239" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -16394,8 +16394,12 @@
       <c r="E240" s="7" t="n">
         <v>0.017226</v>
       </c>
-      <c r="F240" s="7" t="n"/>
-      <c r="G240" s="7" t="n"/>
+      <c r="F240" s="7" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="G240" s="7" t="n">
+        <v>0.016</v>
+      </c>
       <c r="H240" s="6" t="n">
         <v>98.40000000000001</v>
       </c>
@@ -16405,8 +16409,12 @@
       <c r="J240" s="7" t="n">
         <v>-0.013039</v>
       </c>
-      <c r="K240" s="7" t="n"/>
-      <c r="L240" s="7" t="n"/>
+      <c r="K240" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L240" s="7" t="n">
+        <v>-0.014</v>
+      </c>
       <c r="M240" s="6" t="n">
         <v>100.5</v>
       </c>
@@ -16416,11 +16424,21 @@
       <c r="O240" s="7" t="n">
         <v>-0.008876</v>
       </c>
-      <c r="P240" s="7" t="n"/>
-      <c r="Q240" s="7" t="n"/>
-      <c r="R240" s="6" t="n"/>
-      <c r="S240" s="7" t="n"/>
-      <c r="T240" s="7" t="n"/>
+      <c r="P240" s="7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="Q240" s="7" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="R240" s="6" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="S240" s="7" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="T240" s="7" t="n">
+        <v>0.04</v>
+      </c>
       <c r="U240" s="8" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -16433,12 +16451,12 @@
       </c>
       <c r="W240" s="8" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X240" s="8" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -16460,8 +16478,12 @@
       <c r="E241" s="10" t="n">
         <v>0.040256</v>
       </c>
-      <c r="F241" s="10" t="n"/>
-      <c r="G241" s="10" t="n"/>
+      <c r="F241" s="10" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="G241" s="10" t="n">
+        <v>0.041</v>
+      </c>
       <c r="H241" s="9" t="n">
         <v>98.2</v>
       </c>
@@ -16471,8 +16493,12 @@
       <c r="J241" s="10" t="n">
         <v>-0.010081</v>
       </c>
-      <c r="K241" s="10" t="n"/>
-      <c r="L241" s="10" t="n"/>
+      <c r="K241" s="10" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="L241" s="10" t="n">
+        <v>-0.01</v>
+      </c>
       <c r="M241" s="9" t="n">
         <v>97.5</v>
       </c>
@@ -16482,11 +16508,21 @@
       <c r="O241" s="10" t="n">
         <v>-0.010152</v>
       </c>
-      <c r="P241" s="10" t="n"/>
-      <c r="Q241" s="10" t="n"/>
-      <c r="R241" s="9" t="n"/>
-      <c r="S241" s="10" t="n"/>
-      <c r="T241" s="10" t="n"/>
+      <c r="P241" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q241" s="10" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="R241" s="9" t="n">
+        <v>119.1</v>
+      </c>
+      <c r="S241" s="10" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="T241" s="10" t="n">
+        <v>0.027</v>
+      </c>
       <c r="U241" s="11" t="inlineStr">
         <is>
           <t>Definitivo</t>
@@ -16499,12 +16535,12 @@
       </c>
       <c r="W241" s="11" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_10.pdf</t>
         </is>
       </c>
       <c r="X241" s="11" t="inlineStr">
         <is>
-          <t>17 de agosto de 2026</t>
+          <t>16 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -16617,28 +16653,28 @@
         </is>
       </c>
       <c r="C5" s="9" t="n">
-        <v>101.6</v>
+        <v>100.1</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>0.019</v>
+        <v>-0.014</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>104.7</v>
+        <v>104</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>-0.001</v>
+        <v>-0.005</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>104.1</v>
+        <v>104.3</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>0.008</v>
+        <v>-0.004</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>114.3</v>
+        <v>111.5</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>0.052</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="6">
@@ -16653,28 +16689,28 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>107.3</v>
+        <v>108.7</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>116.5</v>
+        <v>115.8</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>122.5</v>
+        <v>122.1</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>0.018</v>
+        <v>-0.002</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>105.5</v>
+        <v>104.2</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>0.001</v>
+        <v>-0.017</v>
       </c>
     </row>
     <row r="7">
@@ -16689,28 +16725,28 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>73.59999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>-0.039</v>
+        <v>0.008</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>69.8</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>-0.028</v>
+        <v>-0.02</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>65.5</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.055</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>100.7</v>
+        <v>105.2</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>-0.004</v>
+        <v>-0.016</v>
       </c>
     </row>
     <row r="8">
@@ -16725,28 +16761,28 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>92.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>-0.025</v>
+        <v>-0.023</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>88.90000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>-0.045</v>
+        <v>-0.04</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>80.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>-0.051</v>
+        <v>-0.034</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>121.6</v>
+        <v>126.2</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>-0.001</v>
+        <v>-0.005</v>
       </c>
     </row>
     <row r="9">
@@ -16761,28 +16797,28 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>66.8</v>
+        <v>68.3</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>-0.019</v>
+        <v>-0.039</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>79.3</v>
+        <v>76.3</v>
       </c>
       <c r="F9" s="10" t="n">
         <v>-0.026</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>73</v>
+        <v>72.3</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>-0.021</v>
+        <v>-0.031</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>122.5</v>
+        <v>120.1</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.008</v>
+        <v>-0.006999999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -16797,28 +16833,28 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>81.59999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="D10" s="7" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="J10" s="7" t="n">
         <v>0.026</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>-0.026</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>78.59999999999999</v>
-      </c>
-      <c r="H10" s="7" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>112.2</v>
-      </c>
-      <c r="J10" s="7" t="n">
-        <v>0.045</v>
       </c>
     </row>
     <row r="11">
@@ -16833,28 +16869,28 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>82.09999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>-0.026</v>
+        <v>0.013</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>77.3</v>
+        <v>80.2</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>-0.024</v>
+        <v>0.014</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>71.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>-0.01</v>
+        <v>0.011</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>128.6</v>
+        <v>115.6</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>-0.002</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="12">
@@ -16869,28 +16905,28 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>97</v>
+        <v>95.7</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>-0.001</v>
+        <v>-0.014</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>102.9</v>
+        <v>102.6</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>-0.03700000000000001</v>
+        <v>-0.028</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>101.9</v>
+        <v>102.3</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>-0.025</v>
+        <v>-0.034</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>120</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>0.022</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="13">
@@ -16905,25 +16941,25 @@
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>105.1</v>
+        <v>103.3</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>0.019</v>
+        <v>-0.023</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>92.7</v>
+        <v>89.3</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.012</v>
+        <v>-0.019</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>91.40000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.016</v>
+        <v>-0.025</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="J13" s="10" t="n">
         <v>0.032</v>
@@ -16941,28 +16977,28 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>156.8</v>
+        <v>189.3</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>-0.05</v>
+        <v>0.235</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>96.5</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="F14" s="7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="J14" s="7" t="n">
         <v>0.003</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="H14" s="7" t="n">
-        <v>0.009000000000000001</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="J14" s="7" t="n">
-        <v>0.006</v>
       </c>
     </row>
     <row r="15">
@@ -16977,28 +17013,28 @@
         </is>
       </c>
       <c r="C15" s="9" t="n">
-        <v>95.5</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>0.051</v>
+        <v>0.022</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>107.4</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>-0.01</v>
+        <v>-0.006</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>108.1</v>
+        <v>109.2</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.005</v>
+        <v>-0.004</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>89.7</v>
+        <v>89.2</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="16">
@@ -17013,28 +17049,28 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>101.1</v>
+        <v>101.6</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>-0.023</v>
+        <v>-0.017</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>99.7</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>-0.03</v>
+        <v>-0.027</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>98</v>
+        <v>96.7</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>-0.026</v>
+        <v>-0.045</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>122.1</v>
+        <v>122</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="17">
@@ -17049,28 +17085,28 @@
         </is>
       </c>
       <c r="C17" s="9" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="E17" s="9" t="n">
         <v>98.2</v>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="F17" s="10" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="H17" s="10" t="n">
         <v>-0.013</v>
       </c>
-      <c r="E17" s="9" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>-0.021</v>
-      </c>
-      <c r="G17" s="9" t="n">
-        <v>95.40000000000001</v>
-      </c>
-      <c r="H17" s="10" t="n">
-        <v>-0.01</v>
-      </c>
       <c r="I17" s="9" t="n">
-        <v>115.5</v>
+        <v>114</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.028</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="18">
@@ -17085,28 +17121,28 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>98.2</v>
+        <v>101.6</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.03</v>
+        <v>0.038</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>100.7</v>
+        <v>101.5</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>-0.004</v>
+        <v>0.011</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>98.59999999999999</v>
+        <v>100.3</v>
       </c>
       <c r="H18" s="7" t="n">
         <v>0.013</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>110.3</v>
+        <v>111.7</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>0.003</v>
+        <v>-0.006</v>
       </c>
     </row>
     <row r="19">
@@ -17121,28 +17157,28 @@
         </is>
       </c>
       <c r="C19" s="9" t="n">
-        <v>98.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.001</v>
+        <v>-0.009000000000000001</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>99.7</v>
+        <v>99.5</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>-0.019</v>
+        <v>-0.01</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>100.4</v>
+        <v>98.7</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>-0.013</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>123.4</v>
+        <v>121.2</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.011</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="20">
@@ -17157,28 +17193,28 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>143.1</v>
+        <v>137.5</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.038</v>
+        <v>0.04</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>117.7</v>
+        <v>117</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.008</v>
+        <v>0.031</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>116</v>
+        <v>115.7</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>0.004</v>
+        <v>0.017</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>115</v>
+        <v>115.5</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="21">
@@ -17193,28 +17229,28 @@
         </is>
       </c>
       <c r="C21" s="9" t="n">
-        <v>175.4</v>
+        <v>172.9</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.068</v>
+        <v>0.058</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>113.7</v>
+        <v>114.6</v>
       </c>
       <c r="F21" s="10" t="n">
-        <v>0.038</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>108.1</v>
+        <v>107.7</v>
       </c>
       <c r="H21" s="10" t="n">
-        <v>0.053</v>
+        <v>0.004</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>133.2</v>
+        <v>129.8</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.035</v>
+        <v>-0.016</v>
       </c>
     </row>
     <row r="22">
@@ -17229,28 +17265,28 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>125</v>
+        <v>126.5</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>-0.032</v>
+        <v>0.021</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>105.7</v>
+        <v>107.1</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>-0.027</v>
+        <v>-0.003</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>106</v>
+        <v>108.8</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>-0.021</v>
+        <v>0.005</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>136.8</v>
+        <v>134.2</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>0.044</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="23">
@@ -17265,28 +17301,28 @@
         </is>
       </c>
       <c r="C23" s="9" t="n">
-        <v>112.2</v>
+        <v>111</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>-0.034</v>
+        <v>0.017</v>
       </c>
       <c r="E23" s="9" t="n">
         <v>91.7</v>
       </c>
       <c r="F23" s="10" t="n">
-        <v>-0.035</v>
+        <v>-0.019</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>92.2</v>
+        <v>90.2</v>
       </c>
       <c r="H23" s="10" t="n">
-        <v>0</v>
+        <v>-0.012</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>118.5</v>
+        <v>120.3</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>0.035</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="24">
@@ -17301,28 +17337,28 @@
         </is>
       </c>
       <c r="C24" s="6" t="n">
-        <v>91.5</v>
+        <v>88.2</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>-0.039</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>77</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>-0.048</v>
+        <v>-0.05599999999999999</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>77.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>139.2</v>
+        <v>139.6</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>0.027</v>
+        <v>0.04099999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -17337,28 +17373,28 @@
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>119.3</v>
+        <v>117.4</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>-0.013</v>
+        <v>-0.038</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>108.9</v>
+        <v>107.8</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>-0.017</v>
+        <v>-0.023</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>107.6</v>
+        <v>107.7</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>-0.006999999999999999</v>
+        <v>0.002</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>144.1</v>
+        <v>142.2</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.038</v>
+        <v>0.033</v>
       </c>
     </row>
   </sheetData>
